--- a/t1_confection/Shares_PET_OIL_Split.xlsx
+++ b/t1_confection/Shares_PET_OIL_Split.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SharesBAU" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SharesNDC" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SharesBAU" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SharesNDC" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AC78"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="17.88671875" customWidth="1" min="1" max="1"/>
@@ -1031,73 +1031,73 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="P4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="R4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="U4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="V4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="W4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="Y4" s="8" t="n">
         <v>0</v>
@@ -1122,73 +1122,73 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="Q5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="S5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="W5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="X5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="Y5" s="8" t="n">
         <v>1</v>
@@ -1668,73 +1668,73 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.6843322707664299</v>
+        <v>0</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0.6843322707664298</v>
+        <v>0</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>0.6843322707664299</v>
+        <v>0</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>0.6843322707664298</v>
+        <v>0</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.6843322707664299</v>
+        <v>0</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>0.6843322707664299</v>
+        <v>0</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.6843322707664298</v>
+        <v>0</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.6843322707664298</v>
+        <v>0</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>0.6843322707664299</v>
+        <v>0</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>0.6843322707664298</v>
+        <v>0</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.6843322707664299</v>
+        <v>0</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0.6843322707664299</v>
+        <v>0</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>0.6843322707664299</v>
+        <v>0</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>0.6843322707664299</v>
+        <v>0</v>
       </c>
       <c r="P11" s="8" t="n">
-        <v>0.6843322707664298</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>0.6843322707664299</v>
+        <v>0</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>0.6843322707664299</v>
+        <v>0</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>0.6843322707664299</v>
+        <v>0</v>
       </c>
       <c r="T11" s="8" t="n">
-        <v>0.6843322707664299</v>
+        <v>0</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>0.6843322707664298</v>
+        <v>0</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>0.6843322707664299</v>
+        <v>0</v>
       </c>
       <c r="W11" s="8" t="n">
-        <v>0.6843322707664299</v>
+        <v>0</v>
       </c>
       <c r="X11" s="8" t="n">
-        <v>0.6843322707664298</v>
+        <v>0</v>
       </c>
       <c r="Y11" s="8" t="n">
         <v>0.6843322707664298</v>
@@ -1759,73 +1759,73 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>1</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>1</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>1</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>1</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>1</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>1</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>1</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>1</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>1</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>1</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>0</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>0</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>0</v>
       </c>
       <c r="P12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>0</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>0</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>0</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>0</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>0</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>0</v>
       </c>
       <c r="W12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>0</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="8" t="n">
         <v>0.3156677292335702</v>
@@ -2123,73 +2123,73 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>0.3620001670139329</v>
+        <v>1</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.4528924721471992</v>
+        <v>1</v>
       </c>
       <c r="N16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="P16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="R16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="S16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="T16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="U16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="X16" s="8" t="n">
-        <v>0.4528924721471991</v>
+        <v>1</v>
       </c>
       <c r="Y16" s="8" t="n">
         <v>0.4528924721471991</v>
@@ -2214,73 +2214,73 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>0.6379998329860671</v>
+        <v>0</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>0.5471075278528008</v>
+        <v>0</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>0.5471075278528009</v>
+        <v>0</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>0.5471075278528009</v>
+        <v>0</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.5471075278528009</v>
+        <v>0</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>0.5471075278528009</v>
+        <v>0</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.5471075278528009</v>
+        <v>0</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.5471075278528008</v>
+        <v>0</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>0.5471075278528009</v>
+        <v>0</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>0.5471075278528009</v>
+        <v>0</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0.5471075278528009</v>
+        <v>0</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.5471075278528009</v>
+        <v>0</v>
       </c>
       <c r="N17" s="8" t="n">
-        <v>0.5471075278528009</v>
+        <v>0</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>0.5471075278528008</v>
+        <v>0</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>0.5471075278528009</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="8" t="n">
-        <v>0.5471075278528009</v>
+        <v>0</v>
       </c>
       <c r="R17" s="8" t="n">
-        <v>0.5471075278528008</v>
+        <v>0</v>
       </c>
       <c r="S17" s="8" t="n">
-        <v>0.5471075278528009</v>
+        <v>0</v>
       </c>
       <c r="T17" s="8" t="n">
-        <v>0.5471075278528008</v>
+        <v>0</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>0.5471075278528009</v>
+        <v>0</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>0.5471075278528009</v>
+        <v>0</v>
       </c>
       <c r="W17" s="8" t="n">
-        <v>0.5471075278528008</v>
+        <v>0</v>
       </c>
       <c r="X17" s="8" t="n">
-        <v>0.5471075278528009</v>
+        <v>0</v>
       </c>
       <c r="Y17" s="8" t="n">
         <v>0.5471075278528008</v>
@@ -2487,73 +2487,73 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>0.004576412279080361</v>
+        <v>0.0005068477580788359</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>0.0005068477580788359</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>0.0005068477580788359</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>0.004576412279080361</v>
+        <v>0.0005068477580788359</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.004576412279080361</v>
+        <v>1</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.004576412279080361</v>
+        <v>1</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.004576412279080361</v>
+        <v>1</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>0.004576412279080361</v>
+        <v>1</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.004576412279080361</v>
+        <v>1</v>
       </c>
       <c r="N20" s="8" t="n">
-        <v>0.004576412279080361</v>
+        <v>1</v>
       </c>
       <c r="O20" s="8" t="n">
-        <v>0.004576412279080361</v>
+        <v>1</v>
       </c>
       <c r="P20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>0.004576412279080361</v>
+        <v>1</v>
       </c>
       <c r="R20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="S20" s="8" t="n">
-        <v>0.004576412279080361</v>
+        <v>1</v>
       </c>
       <c r="T20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="U20" s="8" t="n">
-        <v>0.004576412279080361</v>
+        <v>1</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>0.004576412279080361</v>
+        <v>1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>0.004576412279080361</v>
+        <v>1</v>
       </c>
       <c r="Y20" s="8" t="n">
         <v>0.004576412279080361</v>
@@ -2578,73 +2578,73 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0.9994931522419211</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0.9994931522419211</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0.9994931522419211</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0.9994931522419211</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.9954235877209195</v>
+        <v>0</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.9954235877209195</v>
+        <v>0</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>0.9954235877209198</v>
+        <v>0</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>0.9954235877209195</v>
+        <v>0</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="O21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="P21" s="8" t="n">
-        <v>0.9954235877209195</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="R21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="S21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="T21" s="8" t="n">
-        <v>0.9954235877209195</v>
+        <v>0</v>
       </c>
       <c r="U21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="V21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="W21" s="8" t="n">
-        <v>0.9954235877209195</v>
+        <v>0</v>
       </c>
       <c r="X21" s="8" t="n">
-        <v>0.9954235877209195</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="8" t="n">
         <v>0.9954235877209197</v>
@@ -2760,73 +2760,73 @@
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>0.1562440181669941</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>0.143920138558713</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>0.1385302893978547</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>0.1385302893978547</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.1385302893978547</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>0.1385302893978546</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0.1385302893978547</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.1385302893978547</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>0.1385302893978547</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>0.1385302893978547</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.1385302893978547</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.1385302893978547</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="N23" s="8" t="n">
-        <v>0.1385302893978547</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="O23" s="8" t="n">
-        <v>0.1385302893978547</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="P23" s="8" t="n">
-        <v>0.1385302893978547</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="Q23" s="8" t="n">
-        <v>0.1385302893978546</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="R23" s="8" t="n">
-        <v>0.1385302893978547</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="S23" s="8" t="n">
-        <v>0.1385302893978547</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="T23" s="8" t="n">
-        <v>0.1385302893978547</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="U23" s="8" t="n">
-        <v>0.1385302893978547</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="V23" s="8" t="n">
-        <v>0.1385302893978546</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="W23" s="8" t="n">
-        <v>0.1385302893978547</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="X23" s="8" t="n">
-        <v>0.1385302893978547</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="8" t="n">
         <v>0.1385302893978546</v>
@@ -2851,73 +2851,73 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>0.519757199124986</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>0.5576367578444866</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>0.574203384123503</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>0.574203384123503</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.574203384123503</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>0.5742033841235029</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0.574203384123503</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.574203384123503</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>0.574203384123503</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>0.5742033841235029</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>0.574203384123503</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.574203384123503</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="N24" s="8" t="n">
-        <v>0.574203384123503</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="O24" s="8" t="n">
-        <v>0.574203384123503</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="P24" s="8" t="n">
-        <v>0.574203384123503</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="Q24" s="8" t="n">
-        <v>0.574203384123503</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="R24" s="8" t="n">
-        <v>0.574203384123503</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="S24" s="8" t="n">
-        <v>0.574203384123503</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="T24" s="8" t="n">
-        <v>0.574203384123503</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>0.574203384123503</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="V24" s="8" t="n">
-        <v>0.5742033841235029</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="W24" s="8" t="n">
-        <v>0.574203384123503</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="X24" s="8" t="n">
-        <v>0.574203384123503</v>
+        <v>1</v>
       </c>
       <c r="Y24" s="8" t="n">
         <v>0.574203384123503</v>
@@ -2942,73 +2942,73 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>0.32399878270802</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>0.2984431035968003</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>0.2872663264786423</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>0.2872663264786423</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.2872663264786423</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>0.2872663264786423</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.2872663264786423</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.2872663264786424</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>0.2872663264786423</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>0.2872663264786423</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.2872663264786423</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.2872663264786423</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>0.2872663264786423</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="O25" s="8" t="n">
-        <v>0.2872663264786423</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="P25" s="8" t="n">
-        <v>0.2872663264786423</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="Q25" s="8" t="n">
-        <v>0.2872663264786423</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="R25" s="8" t="n">
-        <v>0.2872663264786423</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="S25" s="8" t="n">
-        <v>0.2872663264786423</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="T25" s="8" t="n">
-        <v>0.2872663264786423</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>0.2872663264786423</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="V25" s="8" t="n">
-        <v>0.2872663264786423</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="W25" s="8" t="n">
-        <v>0.2872663264786423</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="X25" s="8" t="n">
-        <v>0.2872663264786423</v>
+        <v>0</v>
       </c>
       <c r="Y25" s="8" t="n">
         <v>0.2872663264786423</v>
@@ -3318,61 +3318,61 @@
         <v>1</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29" s="8" t="n">
         <v>1</v>
@@ -3579,73 +3579,73 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.09758006606823971</v>
       </c>
       <c r="C32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.09758006606823971</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.09758006606823971</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.09758006606823971</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.09758006606823971</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.09758006606823971</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.1239526065995352</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.2968175826385517</v>
+        <v>0.1239526065995352</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.1674567623801365</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.1674567623801365</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.1674567623801365</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.1988330827399963</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>0.2968175826385517</v>
+        <v>0.1988330827399963</v>
       </c>
       <c r="O32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.1988330827399963</v>
       </c>
       <c r="P32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.1988330827399963</v>
       </c>
       <c r="Q32" s="8" t="n">
-        <v>0.2968175826385517</v>
+        <v>0.2408485411952467</v>
       </c>
       <c r="R32" s="8" t="n">
-        <v>0.2968175826385517</v>
+        <v>0.7194573122434513</v>
       </c>
       <c r="S32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.7194573122434513</v>
       </c>
       <c r="T32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.7194573122434513</v>
       </c>
       <c r="U32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.7194573122434513</v>
       </c>
       <c r="V32" s="8" t="n">
-        <v>0.2968175826385517</v>
+        <v>0.7194573122434513</v>
       </c>
       <c r="W32" s="8" t="n">
-        <v>0.2968175826385517</v>
+        <v>1</v>
       </c>
       <c r="X32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>1</v>
       </c>
       <c r="Y32" s="8" t="n">
         <v>0.2968175826385517</v>
@@ -3670,73 +3670,73 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.9024199339317603</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>0.7031824173614483</v>
+        <v>0.9024199339317603</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.9024199339317603</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.9024199339317603</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.9024199339317603</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>0.7031824173614485</v>
+        <v>0.9024199339317603</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.8760473934004648</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.8760473934004648</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.8325432376198635</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.8325432376198635</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.8325432376198635</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.8011669172600038</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.8011669172600038</v>
       </c>
       <c r="O33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.8011669172600038</v>
       </c>
       <c r="P33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.8011669172600038</v>
       </c>
       <c r="Q33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.7591514588047534</v>
       </c>
       <c r="R33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.2805426877565486</v>
       </c>
       <c r="S33" s="8" t="n">
-        <v>0.7031824173614483</v>
+        <v>0.2805426877565486</v>
       </c>
       <c r="T33" s="8" t="n">
-        <v>0.7031824173614485</v>
+        <v>0.2805426877565486</v>
       </c>
       <c r="U33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.2805426877565486</v>
       </c>
       <c r="V33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.2805426877565486</v>
       </c>
       <c r="W33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0</v>
       </c>
       <c r="X33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0</v>
       </c>
       <c r="Y33" s="8" t="n">
         <v>0.7031824173614484</v>
@@ -3852,73 +3852,73 @@
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>0.7537811488232631</v>
+        <v>1</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>0.7537811488232631</v>
+        <v>1</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>0.7537811488232631</v>
+        <v>1</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>0.4766520519555022</v>
+        <v>1</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.4766520519555023</v>
+        <v>1</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>0.4766520519555023</v>
+        <v>1</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.4766520519555023</v>
+        <v>1</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.3829560471176715</v>
+        <v>1</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>0.3829560471176715</v>
+        <v>1</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>0.3829560471176715</v>
+        <v>1</v>
       </c>
       <c r="N35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="O35" s="8" t="n">
-        <v>0.3829560471176715</v>
+        <v>1</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="R35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="S35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="T35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="U35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="V35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="W35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="Y35" s="8" t="n">
         <v>0.3829560471176714</v>
@@ -3943,73 +3943,73 @@
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>0.2462188511767369</v>
+        <v>0</v>
       </c>
       <c r="C36" s="8" t="n">
-        <v>0.2462188511767369</v>
+        <v>0</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>0.2462188511767369</v>
+        <v>0</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>0.5233479480444977</v>
+        <v>0</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.5233479480444978</v>
+        <v>0</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>0.5233479480444978</v>
+        <v>0</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0.5233479480444978</v>
+        <v>0</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.6170439528823286</v>
+        <v>0</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>0.6170439528823286</v>
+        <v>0</v>
       </c>
       <c r="N36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="O36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="R36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="S36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="T36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="U36" s="8" t="n">
-        <v>0.6170439528823286</v>
+        <v>0</v>
       </c>
       <c r="V36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="W36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>0.6170439528823286</v>
+        <v>0</v>
       </c>
       <c r="Y36" s="8" t="n">
         <v>0.6170439528823285</v>
@@ -4216,73 +4216,73 @@
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>0.2885710160721431</v>
+        <v>0.7914934534655548</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>0.2885710160721431</v>
+        <v>0.7914934534655548</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>0.2885710160721431</v>
+        <v>0.7914934534655548</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>0.2885710160721431</v>
+        <v>0.7914934534655548</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.2885710160721432</v>
+        <v>0</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>0.3247181760056324</v>
+        <v>0</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0.3247181760056324</v>
+        <v>0</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.3247181760056324</v>
+        <v>0</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>0.3247181760056324</v>
+        <v>0</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>0.3247181760056324</v>
+        <v>0</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0.3247181760056324</v>
+        <v>0</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>0.3247181760056324</v>
+        <v>0</v>
       </c>
       <c r="N39" s="8" t="n">
-        <v>0.3247181760056324</v>
+        <v>0</v>
       </c>
       <c r="O39" s="8" t="n">
-        <v>0.3247181760056324</v>
+        <v>0</v>
       </c>
       <c r="P39" s="8" t="n">
-        <v>0.3247181760056324</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="8" t="n">
-        <v>0.3247181760056324</v>
+        <v>0</v>
       </c>
       <c r="R39" s="8" t="n">
-        <v>0.3247181760056324</v>
+        <v>0</v>
       </c>
       <c r="S39" s="8" t="n">
-        <v>0.3247181760056324</v>
+        <v>0</v>
       </c>
       <c r="T39" s="8" t="n">
-        <v>0.3247181760056324</v>
+        <v>0</v>
       </c>
       <c r="U39" s="8" t="n">
-        <v>0.3247181760056324</v>
+        <v>0</v>
       </c>
       <c r="V39" s="8" t="n">
-        <v>0.3247181760056324</v>
+        <v>0</v>
       </c>
       <c r="W39" s="8" t="n">
-        <v>0.3247181760056324</v>
+        <v>0</v>
       </c>
       <c r="X39" s="8" t="n">
-        <v>0.3247181760056324</v>
+        <v>0</v>
       </c>
       <c r="Y39" s="8" t="n">
         <v>0.3247181760056324</v>
@@ -4307,73 +4307,73 @@
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>0.7114289839278568</v>
+        <v>0.2085065465344452</v>
       </c>
       <c r="C40" s="8" t="n">
-        <v>0.7114289839278568</v>
+        <v>0.2085065465344452</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>0.7114289839278568</v>
+        <v>0.2085065465344452</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>0.7114289839278568</v>
+        <v>0.2085065465344452</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>0.7114289839278568</v>
+        <v>1</v>
       </c>
       <c r="G40" s="8" t="n">
-        <v>0.6752818239943676</v>
+        <v>1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>0.6752818239943676</v>
+        <v>1</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.6752818239943676</v>
+        <v>1</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>0.6752818239943675</v>
+        <v>1</v>
       </c>
       <c r="K40" s="8" t="n">
-        <v>0.6752818239943676</v>
+        <v>1</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>0.6752818239943675</v>
+        <v>1</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>0.6752818239943675</v>
+        <v>1</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>0.6752818239943675</v>
+        <v>1</v>
       </c>
       <c r="O40" s="8" t="n">
-        <v>0.6752818239943675</v>
+        <v>1</v>
       </c>
       <c r="P40" s="8" t="n">
-        <v>0.6752818239943675</v>
+        <v>1</v>
       </c>
       <c r="Q40" s="8" t="n">
-        <v>0.6752818239943675</v>
+        <v>1</v>
       </c>
       <c r="R40" s="8" t="n">
-        <v>0.6752818239943675</v>
+        <v>1</v>
       </c>
       <c r="S40" s="8" t="n">
-        <v>0.6752818239943675</v>
+        <v>1</v>
       </c>
       <c r="T40" s="8" t="n">
-        <v>0.6752818239943675</v>
+        <v>1</v>
       </c>
       <c r="U40" s="8" t="n">
-        <v>0.6752818239943675</v>
+        <v>1</v>
       </c>
       <c r="V40" s="8" t="n">
-        <v>0.6752818239943675</v>
+        <v>1</v>
       </c>
       <c r="W40" s="8" t="n">
-        <v>0.6752818239943675</v>
+        <v>1</v>
       </c>
       <c r="X40" s="8" t="n">
-        <v>0.6752818239943676</v>
+        <v>1</v>
       </c>
       <c r="Y40" s="8" t="n">
         <v>0.6752818239943676</v>
@@ -4774,61 +4774,61 @@
         <v>1</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="8" t="n">
         <v>1</v>
@@ -5035,73 +5035,73 @@
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>0.316365492973478</v>
+        <v>0.2875199410970671</v>
       </c>
       <c r="C48" s="8" t="n">
-        <v>0.316365492973478</v>
+        <v>0.2875199410970671</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>0.316365492973478</v>
+        <v>0.2875199410970671</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>0.316365492973478</v>
+        <v>0.2875199410970671</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>0.230204185596288</v>
+        <v>0</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>0.230204185596288</v>
+        <v>0</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>0.2302041855962881</v>
+        <v>0</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.230204185596288</v>
+        <v>0</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>0.2302041855962881</v>
+        <v>0</v>
       </c>
       <c r="K48" s="8" t="n">
-        <v>0.230204185596288</v>
+        <v>0</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>0.2302041855962881</v>
+        <v>0</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>0.2302041855962881</v>
+        <v>0</v>
       </c>
       <c r="N48" s="8" t="n">
-        <v>0.230204185596288</v>
+        <v>0</v>
       </c>
       <c r="O48" s="8" t="n">
-        <v>0.230204185596288</v>
+        <v>0</v>
       </c>
       <c r="P48" s="8" t="n">
-        <v>0.230204185596288</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="8" t="n">
-        <v>0.230204185596288</v>
+        <v>0</v>
       </c>
       <c r="R48" s="8" t="n">
-        <v>0.230204185596288</v>
+        <v>0</v>
       </c>
       <c r="S48" s="8" t="n">
-        <v>0.2302041855962881</v>
+        <v>0</v>
       </c>
       <c r="T48" s="8" t="n">
-        <v>0.230204185596288</v>
+        <v>0</v>
       </c>
       <c r="U48" s="8" t="n">
-        <v>0.230204185596288</v>
+        <v>0</v>
       </c>
       <c r="V48" s="8" t="n">
-        <v>0.230204185596288</v>
+        <v>0</v>
       </c>
       <c r="W48" s="8" t="n">
-        <v>0.230204185596288</v>
+        <v>0</v>
       </c>
       <c r="X48" s="8" t="n">
-        <v>0.2302041855962881</v>
+        <v>0</v>
       </c>
       <c r="Y48" s="8" t="n">
         <v>0.230204185596288</v>
@@ -5126,73 +5126,73 @@
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>0.683634507026522</v>
+        <v>0.7124800589029329</v>
       </c>
       <c r="C49" s="8" t="n">
-        <v>0.683634507026522</v>
+        <v>0.7124800589029329</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>0.683634507026522</v>
+        <v>0.7124800589029329</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>0.683634507026522</v>
+        <v>0.7124800589029329</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.7697958144037119</v>
+        <v>0</v>
       </c>
       <c r="G49" s="8" t="n">
-        <v>0.7697958144037119</v>
+        <v>0</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>0.7697958144037119</v>
+        <v>0</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.7697958144037119</v>
+        <v>0</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>0.769795814403712</v>
+        <v>0</v>
       </c>
       <c r="K49" s="8" t="n">
-        <v>0.7697958144037119</v>
+        <v>0</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>0.769795814403712</v>
+        <v>0</v>
       </c>
       <c r="M49" s="8" t="n">
-        <v>0.7697958144037119</v>
+        <v>0</v>
       </c>
       <c r="N49" s="8" t="n">
-        <v>0.7697958144037119</v>
+        <v>0</v>
       </c>
       <c r="O49" s="8" t="n">
-        <v>0.7697958144037119</v>
+        <v>0</v>
       </c>
       <c r="P49" s="8" t="n">
-        <v>0.769795814403712</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="8" t="n">
-        <v>0.7697958144037119</v>
+        <v>0</v>
       </c>
       <c r="R49" s="8" t="n">
-        <v>0.7697958144037119</v>
+        <v>0</v>
       </c>
       <c r="S49" s="8" t="n">
-        <v>0.7697958144037119</v>
+        <v>0</v>
       </c>
       <c r="T49" s="8" t="n">
-        <v>0.7697958144037119</v>
+        <v>0</v>
       </c>
       <c r="U49" s="8" t="n">
-        <v>0.7697958144037119</v>
+        <v>0</v>
       </c>
       <c r="V49" s="8" t="n">
-        <v>0.7697958144037119</v>
+        <v>0</v>
       </c>
       <c r="W49" s="8" t="n">
-        <v>0.769795814403712</v>
+        <v>0</v>
       </c>
       <c r="X49" s="8" t="n">
-        <v>0.7697958144037119</v>
+        <v>0</v>
       </c>
       <c r="Y49" s="8" t="n">
         <v>0.7697958144037119</v>
@@ -5672,73 +5672,73 @@
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="C55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="G55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="J55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="K55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="L55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="M55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="N55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="O55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="P55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="R55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="S55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="T55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="U55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="V55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="W55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="X55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="Y55" s="8" t="n">
         <v>0.3333333333333333</v>
@@ -5763,73 +5763,73 @@
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="C56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="G56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="J56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="K56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="L56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="M56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="N56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="O56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="P56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="Q56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="R56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="S56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="T56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="U56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="V56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="W56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="X56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="Y56" s="8" t="n">
         <v>0.3333333333333333</v>
@@ -5854,73 +5854,73 @@
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="C57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="G57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="J57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="K57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="L57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="M57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="N57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="O57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="P57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="R57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="S57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="T57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="U57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="V57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="W57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="X57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="Y57" s="8" t="n">
         <v>0.3333333333333333</v>
@@ -6148,52 +6148,52 @@
         <v>0</v>
       </c>
       <c r="I60" s="8" t="n">
-        <v>0.4768918783582798</v>
+        <v>0</v>
       </c>
       <c r="J60" s="8" t="n">
-        <v>0.4768918783582798</v>
+        <v>0</v>
       </c>
       <c r="K60" s="8" t="n">
-        <v>0.4768918783582798</v>
+        <v>0</v>
       </c>
       <c r="L60" s="8" t="n">
-        <v>0.4768918783582798</v>
+        <v>0</v>
       </c>
       <c r="M60" s="8" t="n">
-        <v>0.4768918783582798</v>
+        <v>0</v>
       </c>
       <c r="N60" s="8" t="n">
-        <v>0.4768918783582798</v>
+        <v>0</v>
       </c>
       <c r="O60" s="8" t="n">
-        <v>0.4768918783582798</v>
+        <v>0</v>
       </c>
       <c r="P60" s="8" t="n">
-        <v>0.4768918783582798</v>
+        <v>0</v>
       </c>
       <c r="Q60" s="8" t="n">
-        <v>0.4768918783582797</v>
+        <v>0</v>
       </c>
       <c r="R60" s="8" t="n">
-        <v>0.4768918783582797</v>
+        <v>0</v>
       </c>
       <c r="S60" s="8" t="n">
-        <v>0.4768918783582798</v>
+        <v>0</v>
       </c>
       <c r="T60" s="8" t="n">
-        <v>0.4768918783582797</v>
+        <v>0</v>
       </c>
       <c r="U60" s="8" t="n">
-        <v>0.4768918783582798</v>
+        <v>0</v>
       </c>
       <c r="V60" s="8" t="n">
-        <v>0.4768918783582798</v>
+        <v>0</v>
       </c>
       <c r="W60" s="8" t="n">
-        <v>0.4768918783582798</v>
+        <v>0</v>
       </c>
       <c r="X60" s="8" t="n">
-        <v>0.4768918783582798</v>
+        <v>0</v>
       </c>
       <c r="Y60" s="8" t="n">
         <v>0.4768918783582798</v>
@@ -6230,61 +6230,61 @@
         <v>1</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>0.5231081216417202</v>
+        <v>0</v>
       </c>
       <c r="J61" s="8" t="n">
-        <v>0.5231081216417202</v>
+        <v>0</v>
       </c>
       <c r="K61" s="8" t="n">
-        <v>0.5231081216417203</v>
+        <v>0</v>
       </c>
       <c r="L61" s="8" t="n">
-        <v>0.5231081216417202</v>
+        <v>0</v>
       </c>
       <c r="M61" s="8" t="n">
-        <v>0.5231081216417202</v>
+        <v>0</v>
       </c>
       <c r="N61" s="8" t="n">
-        <v>0.5231081216417202</v>
+        <v>0</v>
       </c>
       <c r="O61" s="8" t="n">
-        <v>0.5231081216417202</v>
+        <v>0</v>
       </c>
       <c r="P61" s="8" t="n">
-        <v>0.5231081216417202</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="8" t="n">
-        <v>0.5231081216417202</v>
+        <v>0</v>
       </c>
       <c r="R61" s="8" t="n">
-        <v>0.5231081216417202</v>
+        <v>0</v>
       </c>
       <c r="S61" s="8" t="n">
-        <v>0.5231081216417202</v>
+        <v>0</v>
       </c>
       <c r="T61" s="8" t="n">
-        <v>0.5231081216417202</v>
+        <v>0</v>
       </c>
       <c r="U61" s="8" t="n">
-        <v>0.5231081216417202</v>
+        <v>0</v>
       </c>
       <c r="V61" s="8" t="n">
-        <v>0.5231081216417202</v>
+        <v>0</v>
       </c>
       <c r="W61" s="8" t="n">
-        <v>0.5231081216417202</v>
+        <v>0</v>
       </c>
       <c r="X61" s="8" t="n">
-        <v>0.5231081216417203</v>
+        <v>0</v>
       </c>
       <c r="Y61" s="8" t="n">
         <v>0.5231081216417202</v>
@@ -6667,6 +6667,711 @@
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" thickBot="1"/>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Diésel</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" t="n">
+        <v>1</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1</v>
+      </c>
+      <c r="O68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1</v>
+      </c>
+      <c r="X68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Fuel oil</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Búnker</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Diésel</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1</v>
+      </c>
+      <c r="N72" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
+      <c r="W72" t="n">
+        <v>1</v>
+      </c>
+      <c r="X72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Fuel oil</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Búnker</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Diésel</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.2812307902907976</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.2812307902907976</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.2812307902907976</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.2812307902907976</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>1</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
+      <c r="S76" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
+      </c>
+      <c r="V76" t="n">
+        <v>1</v>
+      </c>
+      <c r="W76" t="n">
+        <v>1</v>
+      </c>
+      <c r="X76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Fuel oil</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.7187692097092024</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.7187692097092024</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.7187692097092024</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.7187692097092024</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Búnker</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="79" ht="15" customHeight="1" thickBot="1"/>
     <row r="92" ht="15" customHeight="1" thickBot="1"/>
     <row r="105" ht="15" customHeight="1" thickBot="1"/>
@@ -6689,7 +7394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AC78"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col width="21.5546875" bestFit="1" customWidth="1" style="19" min="1" max="1"/>
@@ -6977,73 +7682,73 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="P4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="R4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="U4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="V4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="W4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>0</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="Y4" s="8" t="n">
         <v>0</v>
@@ -7068,73 +7773,73 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="Q5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="S5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="W5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="X5" s="8" t="n">
-        <v>1</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="Y5" s="8" t="n">
         <v>1</v>
@@ -7614,73 +8319,73 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.6843322707664298</v>
+        <v>0</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0.6843322708064022</v>
+        <v>0</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>0.684332270810079</v>
+        <v>0</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>0.6843322708139473</v>
+        <v>0</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.6843322708180222</v>
+        <v>0</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>0.684332270863801</v>
+        <v>0</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.6843322708695135</v>
+        <v>0</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0.9998855872477651</v>
+        <v>0</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>0.9998855871684083</v>
+        <v>0</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>0.9998855872997913</v>
+        <v>0</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.9998855872170135</v>
+        <v>0</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0.9998855871287937</v>
+        <v>0</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>0.9998855872722539</v>
+        <v>0</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>0.9998855871797698</v>
+        <v>0</v>
       </c>
       <c r="P11" s="8" t="n">
-        <v>0.9998855873355232</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>0.999885587238433</v>
+        <v>0</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>0.999885587133736</v>
+        <v>0</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>0.9998855873067375</v>
+        <v>0</v>
       </c>
       <c r="T11" s="8" t="n">
-        <v>0.9998855873067374</v>
+        <v>0</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>0.9998855873067375</v>
+        <v>0</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>0.9998855873067375</v>
+        <v>0</v>
       </c>
       <c r="W11" s="8" t="n">
-        <v>0.9998855873067374</v>
+        <v>0</v>
       </c>
       <c r="X11" s="8" t="n">
-        <v>0.9998855873067375</v>
+        <v>0</v>
       </c>
       <c r="Y11" s="8" t="n">
         <v>0.9998855873067374</v>
@@ -7705,73 +8410,73 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>0.3156677292335702</v>
+        <v>1</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>0.3156677291935978</v>
+        <v>1</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>0.3156677291899209</v>
+        <v>1</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>0.3156677291860528</v>
+        <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0.3156677291819779</v>
+        <v>1</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.3156677291361989</v>
+        <v>1</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0.3156677291304865</v>
+        <v>1</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.0001144127522348248</v>
+        <v>1</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>0.0001144128315917754</v>
+        <v>1</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>0.0001144127002087828</v>
+        <v>1</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0.0001144127829865552</v>
+        <v>1</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.0001144128712063544</v>
+        <v>0</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>0.0001144127277460571</v>
+        <v>0</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>0.0001144128202301766</v>
+        <v>0</v>
       </c>
       <c r="P12" s="8" t="n">
-        <v>0.0001144126644768023</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>0.0001144127615669509</v>
+        <v>0</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>0.0001144128662640045</v>
+        <v>0</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>0.0001144126932625756</v>
+        <v>0</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>0.0001144126932625756</v>
+        <v>0</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>0.0001144126932625756</v>
+        <v>0</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>0.0001144126932625756</v>
+        <v>0</v>
       </c>
       <c r="W12" s="8" t="n">
-        <v>0.0001144126932625756</v>
+        <v>0</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>0.0001144126932625756</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="8" t="n">
         <v>0.0001144126932625756</v>
@@ -8069,73 +8774,73 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>0.000188804241046922</v>
+        <v>1</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>0.0002754282288961434</v>
+        <v>1</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>0.0002754282288961435</v>
+        <v>1</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>0.0002754282288961435</v>
+        <v>1</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.0002754282288961434</v>
+        <v>1</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>0.0002754282288961434</v>
+        <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0.0002754282288961434</v>
+        <v>1</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0.0002754282288961434</v>
+        <v>1</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>0.0002754282288961435</v>
+        <v>1</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>0.0002754282288961434</v>
+        <v>1</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0.0002754282288961434</v>
+        <v>1</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0.0002754282288961435</v>
+        <v>1</v>
       </c>
       <c r="N16" s="8" t="n">
-        <v>0.0002754282288961434</v>
+        <v>1</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>0.0002754282288961434</v>
+        <v>1</v>
       </c>
       <c r="P16" s="8" t="n">
-        <v>0.0002754282288961435</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>0.0002754282288961434</v>
+        <v>1</v>
       </c>
       <c r="R16" s="8" t="n">
-        <v>0.0002754282288961434</v>
+        <v>1</v>
       </c>
       <c r="S16" s="8" t="n">
-        <v>0.0002754282288961434</v>
+        <v>1</v>
       </c>
       <c r="T16" s="8" t="n">
-        <v>0.0002754282288961434</v>
+        <v>1</v>
       </c>
       <c r="U16" s="8" t="n">
-        <v>0.0002754282288961435</v>
+        <v>1</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>0.0002754282288961434</v>
+        <v>1</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>0.0002754282288961434</v>
+        <v>1</v>
       </c>
       <c r="X16" s="8" t="n">
-        <v>0.0002754282288961434</v>
+        <v>1</v>
       </c>
       <c r="Y16" s="8" t="n">
         <v>0.0002754282288961435</v>
@@ -8160,73 +8865,73 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>0.9998111957589529</v>
+        <v>0</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>0.9997245717711039</v>
+        <v>0</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>0.999724571771104</v>
+        <v>0</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>0.999724571771104</v>
+        <v>0</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.9997245717711039</v>
+        <v>0</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>0.9997245717711037</v>
+        <v>0</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>0.9997245717711037</v>
+        <v>0</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>0.999724571771104</v>
+        <v>0</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>0.9997245717711039</v>
+        <v>0</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>0.9997245717711037</v>
+        <v>0</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>0.9997245717711039</v>
+        <v>0</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>0.9997245717711039</v>
+        <v>0</v>
       </c>
       <c r="N17" s="8" t="n">
-        <v>0.9997245717711039</v>
+        <v>0</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>0.9997245717711037</v>
+        <v>0</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>0.9997245717711039</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="8" t="n">
-        <v>0.9997245717711039</v>
+        <v>0</v>
       </c>
       <c r="R17" s="8" t="n">
-        <v>0.9997245717711039</v>
+        <v>0</v>
       </c>
       <c r="S17" s="8" t="n">
-        <v>0.9997245717711039</v>
+        <v>0</v>
       </c>
       <c r="T17" s="8" t="n">
-        <v>0.9997245717711039</v>
+        <v>0</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>0.9997245717711039</v>
+        <v>0</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>0.9997245717711039</v>
+        <v>0</v>
       </c>
       <c r="W17" s="8" t="n">
-        <v>0.9997245717711037</v>
+        <v>0</v>
       </c>
       <c r="X17" s="8" t="n">
-        <v>0.9997245717711039</v>
+        <v>0</v>
       </c>
       <c r="Y17" s="8" t="n">
         <v>0.9997245717711039</v>
@@ -8433,73 +9138,73 @@
         </is>
       </c>
       <c r="B20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>0.0005068477580788359</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>0.0005068477580788359</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>0.004576412279080361</v>
+        <v>0.0005068477580788359</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>0.0005068477580788359</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>0.004576412279080361</v>
+        <v>1</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>0.004576412279080361</v>
+        <v>1</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>0.004576412279080361</v>
+        <v>1</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="N20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="O20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="P20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>0.004576412279080361</v>
+        <v>1</v>
       </c>
       <c r="R20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="S20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="T20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="U20" s="8" t="n">
-        <v>0.004576412279080361</v>
+        <v>1</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>0.004576412279080362</v>
+        <v>1</v>
       </c>
       <c r="Y20" s="8" t="n">
         <v>0.004576412279080362</v>
@@ -8524,73 +9229,73 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0.9994931522419211</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0.9994931522419211</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>0.9954235877209195</v>
+        <v>0.9994931522419211</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0.9994931522419211</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.9954235877209195</v>
+        <v>0</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="O21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="P21" s="8" t="n">
-        <v>0.9954235877209195</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="R21" s="8" t="n">
-        <v>0.9954235877209198</v>
+        <v>0</v>
       </c>
       <c r="S21" s="8" t="n">
-        <v>0.9954235877209195</v>
+        <v>0</v>
       </c>
       <c r="T21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="U21" s="8" t="n">
-        <v>0.9954235877209195</v>
+        <v>0</v>
       </c>
       <c r="V21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="W21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="X21" s="8" t="n">
-        <v>0.9954235877209197</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="8" t="n">
         <v>0.9954235877209197</v>
@@ -8706,73 +9411,73 @@
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>0.195008982433249</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>0.1829352726536146</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="N23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="O23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="P23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="Q23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="R23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="S23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="T23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="U23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="V23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="W23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0.162359273713815</v>
       </c>
       <c r="X23" s="8" t="n">
-        <v>0.1775139358196907</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="8" t="n">
         <v>0.1775139358196907</v>
@@ -8797,73 +9502,73 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>0.4006064294926495</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>0.437717048315358</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>0.4543804573607387</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>0.4543804573607387</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0.4543804573607386</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>0.4543804573607387</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0.4543804573607387</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0.4543804573607387</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>0.4543804573607387</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>0.4543804573607386</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>0.4543804573607387</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>0.4543804573607387</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="N24" s="8" t="n">
-        <v>0.4543804573607387</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="O24" s="8" t="n">
-        <v>0.4543804573607387</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="P24" s="8" t="n">
-        <v>0.4543804573607386</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="Q24" s="8" t="n">
-        <v>0.4543804573607387</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="R24" s="8" t="n">
-        <v>0.4543804573607386</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="S24" s="8" t="n">
-        <v>0.4543804573607386</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="T24" s="8" t="n">
-        <v>0.4543804573607387</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>0.4543804573607387</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="V24" s="8" t="n">
-        <v>0.4543804573607386</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="W24" s="8" t="n">
-        <v>0.4543804573607386</v>
+        <v>0.5009609118409961</v>
       </c>
       <c r="X24" s="8" t="n">
-        <v>0.4543804573607386</v>
+        <v>1</v>
       </c>
       <c r="Y24" s="8" t="n">
         <v>0.4543804573607387</v>
@@ -8888,73 +9593,73 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>0.4043845880741015</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>0.3793476790310273</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>0.3681056068195707</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>0.3681056068195706</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.3681056068195706</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>0.3681056068195707</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.3681056068195707</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>0.3681056068195707</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>0.3681056068195707</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>0.3681056068195706</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0.3681056068195707</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>0.3681056068195707</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>0.3681056068195707</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="O25" s="8" t="n">
-        <v>0.3681056068195707</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="P25" s="8" t="n">
-        <v>0.3681056068195706</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="Q25" s="8" t="n">
-        <v>0.3681056068195707</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="R25" s="8" t="n">
-        <v>0.3681056068195706</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="S25" s="8" t="n">
-        <v>0.3681056068195707</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="T25" s="8" t="n">
-        <v>0.3681056068195707</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>0.3681056068195707</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="V25" s="8" t="n">
-        <v>0.3681056068195707</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="W25" s="8" t="n">
-        <v>0.3681056068195707</v>
+        <v>0.3366798144451889</v>
       </c>
       <c r="X25" s="8" t="n">
-        <v>0.3681056068195706</v>
+        <v>0</v>
       </c>
       <c r="Y25" s="8" t="n">
         <v>0.3681056068195707</v>
@@ -9264,61 +9969,61 @@
         <v>1</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29" s="8" t="n">
         <v>1</v>
@@ -9525,73 +10230,73 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.09758006606823971</v>
       </c>
       <c r="C32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.09758006606823971</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.09758006606823971</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.09758006606823971</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.09758006606823971</v>
       </c>
       <c r="G32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.09758006606823971</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>0.2968175826385516</v>
+        <v>0.1239526065995352</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>0.3073978626574254</v>
+        <v>0.1239526065995352</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>0.3073978626574254</v>
+        <v>0.1674567623801365</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>0.3073978626574254</v>
+        <v>0.1674567623801365</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>0.3073978626574254</v>
+        <v>0.1674567623801365</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>0.3073978626574254</v>
+        <v>0.1988330827399963</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>0.3073978626574254</v>
+        <v>0.1988330827399963</v>
       </c>
       <c r="O32" s="8" t="n">
-        <v>0.3073978626574254</v>
+        <v>0.1988330827399963</v>
       </c>
       <c r="P32" s="8" t="n">
-        <v>0.3073978626574254</v>
+        <v>0.1988330827399963</v>
       </c>
       <c r="Q32" s="8" t="n">
-        <v>0.3073978626574254</v>
+        <v>0.2408485411952467</v>
       </c>
       <c r="R32" s="8" t="n">
-        <v>0.3073978626574254</v>
+        <v>0.7194573122434513</v>
       </c>
       <c r="S32" s="8" t="n">
-        <v>0.3073978626574254</v>
+        <v>0.7194573122434513</v>
       </c>
       <c r="T32" s="8" t="n">
-        <v>0.3073978626574254</v>
+        <v>0.7194573122434513</v>
       </c>
       <c r="U32" s="8" t="n">
-        <v>0.3073978626574254</v>
+        <v>0.7194573122434513</v>
       </c>
       <c r="V32" s="8" t="n">
-        <v>0.3073978626574254</v>
+        <v>0.7194573122434513</v>
       </c>
       <c r="W32" s="8" t="n">
-        <v>0.3073978626574254</v>
+        <v>1</v>
       </c>
       <c r="X32" s="8" t="n">
-        <v>0.3073978626574254</v>
+        <v>1</v>
       </c>
       <c r="Y32" s="8" t="n">
         <v>0.3073978626574254</v>
@@ -9616,73 +10321,73 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.9024199339317603</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>0.7031824173614483</v>
+        <v>0.9024199339317603</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.9024199339317603</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.9024199339317603</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.9024199339317603</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.9024199339317603</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.7031824173614484</v>
+        <v>0.8760473934004648</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>0.6926021373425746</v>
+        <v>0.8760473934004648</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>0.6926021373425746</v>
+        <v>0.8325432376198635</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>0.6926021373425746</v>
+        <v>0.8325432376198635</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>0.6926021373425746</v>
+        <v>0.8325432376198635</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>0.6926021373425746</v>
+        <v>0.8011669172600038</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>0.6926021373425747</v>
+        <v>0.8011669172600038</v>
       </c>
       <c r="O33" s="8" t="n">
-        <v>0.6926021373425746</v>
+        <v>0.8011669172600038</v>
       </c>
       <c r="P33" s="8" t="n">
-        <v>0.6926021373425746</v>
+        <v>0.8011669172600038</v>
       </c>
       <c r="Q33" s="8" t="n">
-        <v>0.6926021373425746</v>
+        <v>0.7591514588047534</v>
       </c>
       <c r="R33" s="8" t="n">
-        <v>0.6926021373425746</v>
+        <v>0.2805426877565486</v>
       </c>
       <c r="S33" s="8" t="n">
-        <v>0.6926021373425745</v>
+        <v>0.2805426877565486</v>
       </c>
       <c r="T33" s="8" t="n">
-        <v>0.6926021373425746</v>
+        <v>0.2805426877565486</v>
       </c>
       <c r="U33" s="8" t="n">
-        <v>0.6926021373425747</v>
+        <v>0.2805426877565486</v>
       </c>
       <c r="V33" s="8" t="n">
-        <v>0.6926021373425746</v>
+        <v>0.2805426877565486</v>
       </c>
       <c r="W33" s="8" t="n">
-        <v>0.6926021373425746</v>
+        <v>0</v>
       </c>
       <c r="X33" s="8" t="n">
-        <v>0.6926021373425746</v>
+        <v>0</v>
       </c>
       <c r="Y33" s="8" t="n">
         <v>0.6926021373425747</v>
@@ -9798,73 +10503,73 @@
         </is>
       </c>
       <c r="B35" s="8" t="n">
-        <v>0.7537811488232631</v>
+        <v>1</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>0.7537811488232631</v>
+        <v>1</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>0.7537811488232632</v>
+        <v>1</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>0.4766520519555022</v>
+        <v>1</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>0.4766520519555022</v>
+        <v>1</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>0.4766520519555022</v>
+        <v>1</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.4766520519555023</v>
+        <v>1</v>
       </c>
       <c r="I35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="N35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="O35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>0.3829560471176715</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="R35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="S35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="T35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="U35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="V35" s="8" t="n">
-        <v>0.3829560471176715</v>
+        <v>1</v>
       </c>
       <c r="W35" s="8" t="n">
-        <v>0.3829560471176714</v>
+        <v>1</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>0.3829560471176715</v>
+        <v>1</v>
       </c>
       <c r="Y35" s="8" t="n">
         <v>0.3829560471176714</v>
@@ -9889,73 +10594,73 @@
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>0.2462188511767369</v>
+        <v>0</v>
       </c>
       <c r="C36" s="8" t="n">
-        <v>0.2462188511767369</v>
+        <v>0</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>0.2462188511767369</v>
+        <v>0</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>0.5233479480444977</v>
+        <v>0</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.5233479480444978</v>
+        <v>0</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>0.5233479480444977</v>
+        <v>0</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0.5233479480444978</v>
+        <v>0</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="M36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="N36" s="8" t="n">
-        <v>0.6170439528823286</v>
+        <v>0</v>
       </c>
       <c r="O36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="R36" s="8" t="n">
-        <v>0.6170439528823286</v>
+        <v>0</v>
       </c>
       <c r="S36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="T36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="U36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="V36" s="8" t="n">
-        <v>0.6170439528823286</v>
+        <v>0</v>
       </c>
       <c r="W36" s="8" t="n">
-        <v>0.6170439528823285</v>
+        <v>0</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>0.6170439528823286</v>
+        <v>0</v>
       </c>
       <c r="Y36" s="8" t="n">
         <v>0.6170439528823285</v>
@@ -10162,73 +10867,73 @@
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>0.2885710160721431</v>
+        <v>0.7914934534655548</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>0.2885710160721431</v>
+        <v>0.7914934534655548</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>0.294159934061677</v>
+        <v>0.7914934534655548</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>0.4157532107934737</v>
+        <v>0.7914934534655548</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.7554643287648113</v>
+        <v>0</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>0.9995642061317979</v>
+        <v>0</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0.999564206131798</v>
+        <v>0</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>0.999564206131798</v>
+        <v>0</v>
       </c>
       <c r="J39" s="8" t="n">
-        <v>0.9995642061317979</v>
+        <v>0</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>0.9995642061317979</v>
+        <v>0</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>0.9995642061317979</v>
+        <v>0</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>0.9995642061317979</v>
+        <v>0</v>
       </c>
       <c r="N39" s="8" t="n">
-        <v>0.9995642061317979</v>
+        <v>0</v>
       </c>
       <c r="O39" s="8" t="n">
-        <v>0.9995642061317979</v>
+        <v>0</v>
       </c>
       <c r="P39" s="8" t="n">
-        <v>0.9995642061317979</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="8" t="n">
-        <v>0.999564206131798</v>
+        <v>0</v>
       </c>
       <c r="R39" s="8" t="n">
-        <v>0.9995642061317979</v>
+        <v>0</v>
       </c>
       <c r="S39" s="8" t="n">
-        <v>0.999564206131798</v>
+        <v>0</v>
       </c>
       <c r="T39" s="8" t="n">
-        <v>0.999564206131798</v>
+        <v>0</v>
       </c>
       <c r="U39" s="8" t="n">
-        <v>0.9995642061317979</v>
+        <v>0</v>
       </c>
       <c r="V39" s="8" t="n">
-        <v>0.999564206131798</v>
+        <v>0</v>
       </c>
       <c r="W39" s="8" t="n">
-        <v>0.999564206131798</v>
+        <v>0</v>
       </c>
       <c r="X39" s="8" t="n">
-        <v>0.9994841792864055</v>
+        <v>0</v>
       </c>
       <c r="Y39" s="8" t="n">
         <v>0.9935687248788743</v>
@@ -10253,73 +10958,73 @@
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>0.7114289839278568</v>
+        <v>0.2085065465344452</v>
       </c>
       <c r="C40" s="8" t="n">
-        <v>0.7114289839278569</v>
+        <v>0.2085065465344452</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>0.7058400659383229</v>
+        <v>0.2085065465344452</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>0.5842467892065264</v>
+        <v>0.2085065465344452</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>0.2445356712351886</v>
+        <v>1</v>
       </c>
       <c r="G40" s="8" t="n">
-        <v>0.0004357938682021106</v>
+        <v>1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>0.0004357938682021105</v>
+        <v>1</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0.0004357938682021106</v>
+        <v>1</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>0.0004357938682021105</v>
+        <v>1</v>
       </c>
       <c r="K40" s="8" t="n">
-        <v>0.0004357938682021106</v>
+        <v>1</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>0.0004357938682021105</v>
+        <v>1</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>0.0004357938682021106</v>
+        <v>1</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>0.0004357938682021106</v>
+        <v>1</v>
       </c>
       <c r="O40" s="8" t="n">
-        <v>0.0004357938682021106</v>
+        <v>1</v>
       </c>
       <c r="P40" s="8" t="n">
-        <v>0.0004357938682021106</v>
+        <v>1</v>
       </c>
       <c r="Q40" s="8" t="n">
-        <v>0.0004357938682021106</v>
+        <v>1</v>
       </c>
       <c r="R40" s="8" t="n">
-        <v>0.0004357938682021105</v>
+        <v>1</v>
       </c>
       <c r="S40" s="8" t="n">
-        <v>0.0004357938682021106</v>
+        <v>1</v>
       </c>
       <c r="T40" s="8" t="n">
-        <v>0.0004357938682021106</v>
+        <v>1</v>
       </c>
       <c r="U40" s="8" t="n">
-        <v>0.0004357938682021105</v>
+        <v>1</v>
       </c>
       <c r="V40" s="8" t="n">
-        <v>0.0004357938682021106</v>
+        <v>1</v>
       </c>
       <c r="W40" s="8" t="n">
-        <v>0.0004357938682021106</v>
+        <v>1</v>
       </c>
       <c r="X40" s="8" t="n">
-        <v>0.0005158207135944949</v>
+        <v>1</v>
       </c>
       <c r="Y40" s="8" t="n">
         <v>0.006431275121125742</v>
@@ -10720,61 +11425,61 @@
         <v>1</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="8" t="n">
         <v>1</v>
@@ -10981,73 +11686,73 @@
         </is>
       </c>
       <c r="B48" s="8" t="n">
-        <v>0.316365492973478</v>
+        <v>0.2875199410970671</v>
       </c>
       <c r="C48" s="8" t="n">
-        <v>0.316365492973478</v>
+        <v>0.2875199410970671</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>0.316365492973478</v>
+        <v>0.2875199410970671</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>0.316365492973478</v>
+        <v>0.2875199410970671</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>0.2302041855962881</v>
+        <v>0</v>
       </c>
       <c r="G48" s="8" t="n">
-        <v>0.2302041855962881</v>
+        <v>0</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>0.2302041855962881</v>
+        <v>0</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>0.000158802783295924</v>
+        <v>0</v>
       </c>
       <c r="J48" s="8" t="n">
-        <v>0.000158802783295924</v>
+        <v>0</v>
       </c>
       <c r="K48" s="8" t="n">
-        <v>0.0001588027832959241</v>
+        <v>0</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>0.0001588027832959241</v>
+        <v>0</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>0.0001588027832959241</v>
+        <v>0</v>
       </c>
       <c r="N48" s="8" t="n">
-        <v>0.0001588027832959241</v>
+        <v>0</v>
       </c>
       <c r="O48" s="8" t="n">
-        <v>0.0001588027832959241</v>
+        <v>0</v>
       </c>
       <c r="P48" s="8" t="n">
-        <v>0.0001588027832959241</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="8" t="n">
-        <v>0.000158802783295924</v>
+        <v>0</v>
       </c>
       <c r="R48" s="8" t="n">
-        <v>0.0001588027832959241</v>
+        <v>0</v>
       </c>
       <c r="S48" s="8" t="n">
-        <v>0.0001588027832959241</v>
+        <v>0</v>
       </c>
       <c r="T48" s="8" t="n">
-        <v>0.0001588027832959241</v>
+        <v>0</v>
       </c>
       <c r="U48" s="8" t="n">
-        <v>0.0002425774356969435</v>
+        <v>0</v>
       </c>
       <c r="V48" s="8" t="n">
-        <v>0.0002425774356969436</v>
+        <v>0</v>
       </c>
       <c r="W48" s="8" t="n">
-        <v>0.0005176034815909327</v>
+        <v>0</v>
       </c>
       <c r="X48" s="8" t="n">
-        <v>0.0005176034815909327</v>
+        <v>0</v>
       </c>
       <c r="Y48" s="8" t="n">
         <v>0.9364583643457793</v>
@@ -11072,73 +11777,73 @@
         </is>
       </c>
       <c r="B49" s="8" t="n">
-        <v>0.683634507026522</v>
+        <v>0.7124800589029329</v>
       </c>
       <c r="C49" s="8" t="n">
-        <v>0.6836345070265221</v>
+        <v>0.7124800589029329</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>0.683634507026522</v>
+        <v>0.7124800589029329</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>0.683634507026522</v>
+        <v>0.7124800589029329</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>0.7697958144037119</v>
+        <v>0</v>
       </c>
       <c r="G49" s="8" t="n">
-        <v>0.769795814403712</v>
+        <v>0</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>0.769795814403712</v>
+        <v>0</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>0.9998411972167041</v>
+        <v>0</v>
       </c>
       <c r="J49" s="8" t="n">
-        <v>0.9998411972167041</v>
+        <v>0</v>
       </c>
       <c r="K49" s="8" t="n">
-        <v>0.9998411972167041</v>
+        <v>0</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>0.9998411972167041</v>
+        <v>0</v>
       </c>
       <c r="M49" s="8" t="n">
-        <v>0.9998411972167042</v>
+        <v>0</v>
       </c>
       <c r="N49" s="8" t="n">
-        <v>0.9998411972167041</v>
+        <v>0</v>
       </c>
       <c r="O49" s="8" t="n">
-        <v>0.9998411972167041</v>
+        <v>0</v>
       </c>
       <c r="P49" s="8" t="n">
-        <v>0.9998411972167042</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="8" t="n">
-        <v>0.9998411972167041</v>
+        <v>0</v>
       </c>
       <c r="R49" s="8" t="n">
-        <v>0.9998411972167041</v>
+        <v>0</v>
       </c>
       <c r="S49" s="8" t="n">
-        <v>0.9998411972167042</v>
+        <v>0</v>
       </c>
       <c r="T49" s="8" t="n">
-        <v>0.9998411972167041</v>
+        <v>0</v>
       </c>
       <c r="U49" s="8" t="n">
-        <v>0.999757422564303</v>
+        <v>0</v>
       </c>
       <c r="V49" s="8" t="n">
-        <v>0.9997574225643031</v>
+        <v>0</v>
       </c>
       <c r="W49" s="8" t="n">
-        <v>0.9994823965184091</v>
+        <v>0</v>
       </c>
       <c r="X49" s="8" t="n">
-        <v>0.9994823965184091</v>
+        <v>0</v>
       </c>
       <c r="Y49" s="8" t="n">
         <v>0.06354163565422064</v>
@@ -11618,73 +12323,73 @@
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="C55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="F55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="G55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="I55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="J55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="K55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="L55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="M55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="N55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="O55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="P55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="R55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="S55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="T55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="U55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="V55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="W55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="X55" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="Y55" s="8" t="n">
         <v>0.3333333333333333</v>
@@ -11709,73 +12414,73 @@
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="C56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="E56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="G56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="I56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="J56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="K56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="L56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="M56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="N56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="O56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="P56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="Q56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="R56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="S56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="T56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="U56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="V56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="W56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="X56" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="Y56" s="8" t="n">
         <v>0.3333333333333333</v>
@@ -11800,73 +12505,73 @@
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="C57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="E57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="G57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="J57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="K57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="L57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="M57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="N57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="O57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="P57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="R57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="S57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="T57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="U57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="V57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="W57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="X57" s="8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="Y57" s="8" t="n">
         <v>0.3333333333333333</v>
@@ -12094,52 +12799,52 @@
         <v>0</v>
       </c>
       <c r="I60" s="8" t="n">
-        <v>0.9999976634611677</v>
+        <v>0</v>
       </c>
       <c r="J60" s="8" t="n">
-        <v>0.9999976634611677</v>
+        <v>0</v>
       </c>
       <c r="K60" s="8" t="n">
-        <v>0.9999976634611678</v>
+        <v>0</v>
       </c>
       <c r="L60" s="8" t="n">
-        <v>0.9999976634611677</v>
+        <v>0</v>
       </c>
       <c r="M60" s="8" t="n">
-        <v>0.9999976634611678</v>
+        <v>0</v>
       </c>
       <c r="N60" s="8" t="n">
-        <v>0.9999976634611678</v>
+        <v>0</v>
       </c>
       <c r="O60" s="8" t="n">
-        <v>0.9999976634611678</v>
+        <v>0</v>
       </c>
       <c r="P60" s="8" t="n">
-        <v>0.9999976634611677</v>
+        <v>0</v>
       </c>
       <c r="Q60" s="8" t="n">
-        <v>0.9999976634611677</v>
+        <v>0</v>
       </c>
       <c r="R60" s="8" t="n">
-        <v>0.9999976634611677</v>
+        <v>0</v>
       </c>
       <c r="S60" s="8" t="n">
-        <v>0.9999976634611677</v>
+        <v>0</v>
       </c>
       <c r="T60" s="8" t="n">
-        <v>0.9999976634611678</v>
+        <v>0</v>
       </c>
       <c r="U60" s="8" t="n">
-        <v>0.9999976634611678</v>
+        <v>0</v>
       </c>
       <c r="V60" s="8" t="n">
-        <v>0.9999976634611677</v>
+        <v>0</v>
       </c>
       <c r="W60" s="8" t="n">
-        <v>0.9999976634611678</v>
+        <v>0</v>
       </c>
       <c r="X60" s="8" t="n">
-        <v>0.9999976634611677</v>
+        <v>0</v>
       </c>
       <c r="Y60" s="8" t="n">
         <v>0.9999976634611678</v>
@@ -12176,61 +12881,61 @@
         <v>1</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" s="8" t="n">
-        <v>2.336538832259928e-06</v>
+        <v>0</v>
       </c>
       <c r="J61" s="8" t="n">
-        <v>2.336538832259928e-06</v>
+        <v>0</v>
       </c>
       <c r="K61" s="8" t="n">
-        <v>2.336538832259928e-06</v>
+        <v>0</v>
       </c>
       <c r="L61" s="8" t="n">
-        <v>2.336538832259928e-06</v>
+        <v>0</v>
       </c>
       <c r="M61" s="8" t="n">
-        <v>2.336538832259928e-06</v>
+        <v>0</v>
       </c>
       <c r="N61" s="8" t="n">
-        <v>2.336538832259928e-06</v>
+        <v>0</v>
       </c>
       <c r="O61" s="8" t="n">
-        <v>2.336538832259928e-06</v>
+        <v>0</v>
       </c>
       <c r="P61" s="8" t="n">
-        <v>2.336538832259928e-06</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="8" t="n">
-        <v>2.336538832259928e-06</v>
+        <v>0</v>
       </c>
       <c r="R61" s="8" t="n">
-        <v>2.336538832259928e-06</v>
+        <v>0</v>
       </c>
       <c r="S61" s="8" t="n">
-        <v>2.336538832259928e-06</v>
+        <v>0</v>
       </c>
       <c r="T61" s="8" t="n">
-        <v>2.336538832259928e-06</v>
+        <v>0</v>
       </c>
       <c r="U61" s="8" t="n">
-        <v>2.336538832259928e-06</v>
+        <v>0</v>
       </c>
       <c r="V61" s="8" t="n">
-        <v>2.336538832259928e-06</v>
+        <v>0</v>
       </c>
       <c r="W61" s="8" t="n">
-        <v>2.336538832259929e-06</v>
+        <v>0</v>
       </c>
       <c r="X61" s="8" t="n">
-        <v>2.336538832259928e-06</v>
+        <v>0</v>
       </c>
       <c r="Y61" s="8" t="n">
         <v>2.336538832259928e-06</v>
@@ -12613,6 +13318,711 @@
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" thickBot="1"/>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Diésel</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" t="n">
+        <v>1</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1</v>
+      </c>
+      <c r="O68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1</v>
+      </c>
+      <c r="X68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Fuel oil</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Búnker</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Diésel</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1</v>
+      </c>
+      <c r="N72" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
+      <c r="W72" t="n">
+        <v>1</v>
+      </c>
+      <c r="X72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Fuel oil</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Búnker</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Diésel</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.2812307902907976</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>1</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
+      <c r="S76" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
+      </c>
+      <c r="V76" t="n">
+        <v>1</v>
+      </c>
+      <c r="W76" t="n">
+        <v>1</v>
+      </c>
+      <c r="X76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Fuel oil</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.7187692097092024</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Búnker</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="79" ht="15" customHeight="1" thickBot="1"/>
     <row r="92" ht="15" customHeight="1" thickBot="1"/>
     <row r="105" ht="15" customHeight="1" thickBot="1"/>
